--- a/georgia_ev_intelligence/outputs/llm_comparison/full_20260505/generations.xlsx
+++ b/georgia_ev_intelligence/outputs/llm_comparison/full_20260505/generations.xlsx
@@ -11025,13 +11025,13 @@
     <col min="1" max="1" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="2" max="2" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="6" width="16.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="6" width="29.14785714285714" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="6" width="15.862142857142858" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="6" width="22.005" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="6" width="66.005" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="6" width="45.29071428571429" customWidth="1" bestFit="1"/>
     <col min="11" max="11" style="6" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="12" max="12" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="13" max="13" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
